--- a/VerveStacks_MYS_grids_kan/vt_vervestacks_MYS_v1.xlsx
+++ b/VerveStacks_MYS_grids_kan/vt_vervestacks_MYS_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_MYS_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{261C95D7-B474-4558-A262-9DDBAD350B95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DF0AE458-0600-4623-9BE6-84BE92A5D345}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{74CB3698-5B1C-4762-B2B5-E48FDC7223BB}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{30195780-43B6-43C1-8616-9827451777C1}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -1844,7 +1844,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FBA7681-3E24-41CC-80BF-E7797B48F52A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{085CC8AC-BE98-45F6-B493-63F82C8F8E2F}">
   <dimension ref="B9:V84"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -6512,7 +6512,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3D402F8-9144-49E4-BB7E-AC47B63DF1B5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59095C0D-9C77-4678-BE69-1C6C9A190BAA}">
   <dimension ref="B9:V35"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -8070,7 +8070,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB73639B-8D4C-4D44-B9ED-7AE6B2A86E4D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8786746D-12B7-4D38-9D44-621108395FE1}">
   <dimension ref="B9:V132"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -13698,7 +13698,7 @@
         <v>33</v>
       </c>
       <c r="M105">
-        <v>0.18688089218129916</v>
+        <v>0.18688089218129919</v>
       </c>
       <c r="O105" t="s">
         <v>178</v>
@@ -13751,7 +13751,7 @@
         <v>33</v>
       </c>
       <c r="M106">
-        <v>0.18688089218129916</v>
+        <v>0.18688089218129919</v>
       </c>
       <c r="O106" t="s">
         <v>178</v>
@@ -13804,7 +13804,7 @@
         <v>33</v>
       </c>
       <c r="M107">
-        <v>0.18688089218129916</v>
+        <v>0.18688089218129919</v>
       </c>
       <c r="O107" t="s">
         <v>178</v>
@@ -14064,7 +14064,7 @@
         <v>14</v>
       </c>
       <c r="R111" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="S111" t="s">
         <v>180</v>
@@ -14126,7 +14126,7 @@
         <v>14</v>
       </c>
       <c r="R112" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="S112" t="s">
         <v>180</v>
@@ -14188,7 +14188,7 @@
         <v>14</v>
       </c>
       <c r="R113" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="S113" t="s">
         <v>180</v>
@@ -14250,7 +14250,7 @@
         <v>14</v>
       </c>
       <c r="R114" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="S114" t="s">
         <v>180</v>
@@ -15003,7 +15003,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DC6DD46-3D7E-4C2F-93D9-33C69BCE49BA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41D25348-AA4D-4CD4-A810-415C0B8B834E}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>
